--- a/artfynd/A 58667-2024 artfynd.xlsx
+++ b/artfynd/A 58667-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104210965</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450282.1670182858</v>
+        <v>450282</v>
       </c>
       <c r="R2" t="n">
-        <v>6431109.842988154</v>
+        <v>6431110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-10-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104210966</v>
+        <v>79742681</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,40 +787,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baskarp, Vg</t>
+          <t>Baskarp kalkbarrskog, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450198.8261693267</v>
+        <v>450182</v>
       </c>
       <c r="R3" t="n">
-        <v>6431194.054516759</v>
+        <v>6431125</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,27 +852,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>grupp med 3 frkr samt 2 ensamma frkr inom ca 4 m2</t>
+          <t>Ca 10 m från ån.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,34 +871,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Niklas Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ida Johansson, Morgan Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104210967</v>
+        <v>80576065</v>
       </c>
       <c r="B4" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,37 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baskarp, Vg</t>
+          <t>Svedån, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450190.859464057</v>
+        <v>450172</v>
       </c>
       <c r="R4" t="n">
-        <v>6431193.624203034</v>
+        <v>6431111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,27 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4 frkr inom ca 2 m2</t>
+          <t>2019-09-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +972,851 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Therese Helgesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104210966</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>450199</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6431194</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>grupp med 3 frkr samt 2 ensamma frkr inom ca 4 m2</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Ida Johansson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Ida Johansson, Morgan Johansson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104210967</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450191</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6431194</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 frkr inom ca 2 m2</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ida Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ida Johansson, Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123246884</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Baskarp, Svedån, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450127</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6431200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127098375</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>450170</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6431136</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127098376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>450172</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6431133</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127098377</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>450175</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6431130</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127098378</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Baskarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>450179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6431135</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Morgan Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>73064092</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svedån Ekebäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>450194</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6431089</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-09-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-09-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Anders Hildingsson, Pontus Axén, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58667-2024 artfynd.xlsx
+++ b/artfynd/A 58667-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104210965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79742681</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80576065</t>
         </is>
       </c>
     </row>
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104210966</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104210967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123246884</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098375</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127098378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,8 +1872,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73064092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>